--- a/test_output/integration_tests/yield_table.xlsx
+++ b/test_output/integration_tests/yield_table.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tpa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>basal_area</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>qmd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mean_dbh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>top_height</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mean_height</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ccf</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sdi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_sdi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>relsdi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>merchantable_volume</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>board_feet</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>site_index</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>initial_tpa</t>
         </is>
@@ -520,25 +508,25 @@
         <v>300</v>
       </c>
       <c r="B2" t="n">
-        <v>0.42</v>
+        <v>0.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5057117843089891</v>
+        <v>0.09999999999999966</v>
       </c>
       <c r="D2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03334925322627221</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>2.493938204873166</v>
+        <v>0.1849785005584436</v>
       </c>
       <c r="I2" t="n">
         <v>480</v>
@@ -550,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.17</v>
+        <v>55.98</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -572,28 +560,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B3" t="n">
-        <v>9.82</v>
+        <v>0.02</v>
       </c>
       <c r="C3" t="n">
-        <v>2.471054293119257</v>
+        <v>0.1004999999999998</v>
       </c>
       <c r="D3" t="n">
-        <v>2.47</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>19.52586103200873</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>19.47</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7829703248418611</v>
+        <v>0.001286347938457306</v>
       </c>
       <c r="H3" t="n">
-        <v>31.28946141365542</v>
+        <v>0.1821143421926082</v>
       </c>
       <c r="I3" t="n">
         <v>480</v>
@@ -605,7 +593,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>142.71</v>
+        <v>54.67</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -627,40 +615,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B4" t="n">
-        <v>26.25</v>
+        <v>0.02</v>
       </c>
       <c r="C4" t="n">
-        <v>4.059984330580397</v>
+        <v>0.1031826830703899</v>
       </c>
       <c r="D4" t="n">
-        <v>4.06</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>31.45541404691291</v>
+        <v>2.682683070390043</v>
       </c>
       <c r="F4" t="n">
-        <v>31.41</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.580593040986829</v>
+        <v>0.001314288429033955</v>
       </c>
       <c r="H4" t="n">
-        <v>68.71704019278643</v>
+        <v>0.1841438762388723</v>
       </c>
       <c r="I4" t="n">
         <v>480</v>
       </c>
       <c r="J4" t="n">
-        <v>1.431605004016384</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>432.41</v>
+        <v>53.01</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -682,43 +670,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B5" t="n">
-        <v>52.63</v>
+        <v>1.2</v>
       </c>
       <c r="C5" t="n">
-        <v>5.76811018449127</v>
+        <v>0.885049681942502</v>
       </c>
       <c r="D5" t="n">
-        <v>5.77</v>
+        <v>0.89</v>
       </c>
       <c r="E5" t="n">
-        <v>42.00774045070173</v>
+        <v>7.424053531606059</v>
       </c>
       <c r="F5" t="n">
-        <v>41.96</v>
+        <v>7.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.419544036814349</v>
+        <v>0.09533492801974973</v>
       </c>
       <c r="H5" t="n">
-        <v>119.9103973679238</v>
+        <v>5.71532735177013</v>
       </c>
       <c r="I5" t="n">
         <v>480</v>
       </c>
       <c r="J5" t="n">
-        <v>2.498133278498413</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>1066.25</v>
+        <v>56.31</v>
       </c>
       <c r="M5" t="n">
-        <v>255.7526486632848</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -737,43 +725,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B6" t="n">
-        <v>82.87</v>
+        <v>5.03</v>
       </c>
       <c r="C6" t="n">
-        <v>7.301655941582509</v>
+        <v>1.830871301418936</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
-        <v>50.42790320539729</v>
+        <v>14.6065891273954</v>
       </c>
       <c r="F6" t="n">
-        <v>50.38</v>
+        <v>14.61</v>
       </c>
       <c r="G6" t="n">
-        <v>3.280728637092667</v>
+        <v>0.4006886487087377</v>
       </c>
       <c r="H6" t="n">
-        <v>172.0426607747431</v>
+        <v>18.02596363095638</v>
       </c>
       <c r="I6" t="n">
         <v>480</v>
       </c>
       <c r="J6" t="n">
-        <v>3.584222099473814</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>1966.93</v>
+        <v>47.5</v>
       </c>
       <c r="M6" t="n">
-        <v>751.7104277614453</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -792,46 +780,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B7" t="n">
-        <v>114.94</v>
+        <v>13.89</v>
       </c>
       <c r="C7" t="n">
-        <v>8.629405522417626</v>
+        <v>3.082086249309318</v>
       </c>
       <c r="D7" t="n">
-        <v>8.619999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="E7" t="n">
-        <v>57.19786617065886</v>
+        <v>24.5397261627109</v>
       </c>
       <c r="F7" t="n">
-        <v>57.14</v>
+        <v>24.54</v>
       </c>
       <c r="G7" t="n">
-        <v>4.149937990712941</v>
+        <v>1.07724573967667</v>
       </c>
       <c r="H7" t="n">
-        <v>223.375606764845</v>
+        <v>40.52571431662009</v>
       </c>
       <c r="I7" t="n">
         <v>480</v>
       </c>
       <c r="J7" t="n">
-        <v>4.653658474267603</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>3063.73</v>
+        <v>119.95</v>
       </c>
       <c r="M7" t="n">
-        <v>1429.093825789228</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>100.1069680200253</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -850,25 +838,25 @@
         <v>600</v>
       </c>
       <c r="B8" t="n">
-        <v>0.86</v>
+        <v>0.03</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5132584573281596</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.5</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06870402644466962</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H8" t="n">
-        <v>5.107880329632408</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I8" t="n">
         <v>480</v>
@@ -880,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>112.34</v>
+        <v>111.96</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -902,40 +890,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B9" t="n">
-        <v>19.57</v>
+        <v>0.03</v>
       </c>
       <c r="C9" t="n">
-        <v>2.470401570951238</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D9" t="n">
-        <v>2.47</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>19.52173010063862</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>19.46</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.559808011720739</v>
+        <v>0.00259903747292395</v>
       </c>
       <c r="H9" t="n">
-        <v>62.34035220330757</v>
+        <v>0.3679579883208992</v>
       </c>
       <c r="I9" t="n">
         <v>480</v>
       </c>
       <c r="J9" t="n">
-        <v>1.298757337568908</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>284.32</v>
+        <v>110.46</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -957,40 +945,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B10" t="n">
-        <v>51.13</v>
+        <v>0.03</v>
       </c>
       <c r="C10" t="n">
-        <v>4.037734846008885</v>
+        <v>0.1031826650033752</v>
       </c>
       <c r="D10" t="n">
-        <v>4.04</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>31.40510572340726</v>
+        <v>2.682665003374817</v>
       </c>
       <c r="F10" t="n">
-        <v>31.35</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>3.092883095523207</v>
+        <v>0.002665598133857893</v>
       </c>
       <c r="H10" t="n">
-        <v>134.1278635642367</v>
+        <v>0.3734747989629788</v>
       </c>
       <c r="I10" t="n">
         <v>480</v>
       </c>
       <c r="J10" t="n">
-        <v>2.794330490921598</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>842.15</v>
+        <v>107.51</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1012,43 +1000,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B11" t="n">
-        <v>94.89</v>
+        <v>2.43</v>
       </c>
       <c r="C11" t="n">
-        <v>5.559033398405213</v>
+        <v>0.8850401254806647</v>
       </c>
       <c r="D11" t="n">
-        <v>5.56</v>
+        <v>0.89</v>
       </c>
       <c r="E11" t="n">
-        <v>41.85921049288094</v>
+        <v>7.423980960176197</v>
       </c>
       <c r="F11" t="n">
-        <v>41.81</v>
+        <v>7.42</v>
       </c>
       <c r="G11" t="n">
-        <v>4.47587443156129</v>
+        <v>0.1933895347508688</v>
       </c>
       <c r="H11" t="n">
-        <v>219.3977879257586</v>
+        <v>11.59374884548608</v>
       </c>
       <c r="I11" t="n">
         <v>480</v>
       </c>
       <c r="J11" t="n">
-        <v>4.570787248453304</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>1923.63</v>
+        <v>114.23</v>
       </c>
       <c r="M11" t="n">
-        <v>416.1111719813493</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1067,43 +1055,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B12" t="n">
-        <v>139.88</v>
+        <v>10.18</v>
       </c>
       <c r="C12" t="n">
-        <v>6.810100972147636</v>
+        <v>1.830273244637624</v>
       </c>
       <c r="D12" t="n">
-        <v>6.81</v>
+        <v>1.83</v>
       </c>
       <c r="E12" t="n">
-        <v>50.14640569664883</v>
+        <v>14.60204750555931</v>
       </c>
       <c r="F12" t="n">
-        <v>50.09</v>
+        <v>14.6</v>
       </c>
       <c r="G12" t="n">
-        <v>5.772261577340355</v>
+        <v>0.8110465260455616</v>
       </c>
       <c r="H12" t="n">
-        <v>298.4946701860059</v>
+        <v>36.49163015851835</v>
       </c>
       <c r="I12" t="n">
         <v>480</v>
       </c>
       <c r="J12" t="n">
-        <v>6.218638962208457</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>3315.26</v>
+        <v>96.12</v>
       </c>
       <c r="M12" t="n">
-        <v>1143.854256396487</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1122,43 +1110,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B13" t="n">
-        <v>180.53</v>
+        <v>28.14</v>
       </c>
       <c r="C13" t="n">
-        <v>7.807557081067749</v>
+        <v>3.079404336882448</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8</v>
+        <v>3.08</v>
       </c>
       <c r="E13" t="n">
-        <v>56.8197967100564</v>
+        <v>24.51058855390398</v>
       </c>
       <c r="F13" t="n">
-        <v>56.76</v>
+        <v>24.51</v>
       </c>
       <c r="G13" t="n">
-        <v>6.875487747971916</v>
+        <v>2.184723948545284</v>
       </c>
       <c r="H13" t="n">
-        <v>364.9947975565192</v>
+        <v>82.14629502722113</v>
       </c>
       <c r="I13" t="n">
         <v>480</v>
       </c>
       <c r="J13" t="n">
-        <v>7.604058282427482</v>
+        <v>1.71138114640044</v>
       </c>
       <c r="K13" t="n">
         <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>4798.98</v>
+        <v>242.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2016.891529195628</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1180,25 +1168,25 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="C14" t="n">
-        <v>0.518052074779115</v>
+        <v>0.09999999999999966</v>
       </c>
       <c r="D14" t="n">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03499667629129826</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>2.592331813441661</v>
+        <v>0.1849785005584436</v>
       </c>
       <c r="I14" t="n">
         <v>480</v>
@@ -1210,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>56.18</v>
+        <v>55.98</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1232,40 +1220,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B15" t="n">
-        <v>17.46</v>
+        <v>0.02</v>
       </c>
       <c r="C15" t="n">
-        <v>3.288514411188279</v>
+        <v>0.1004999999999998</v>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>25.73340306615325</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.271752820240926</v>
+        <v>0.001290738204458867</v>
       </c>
       <c r="H15" t="n">
-        <v>49.66795841653555</v>
+        <v>0.1827358928485557</v>
       </c>
       <c r="I15" t="n">
         <v>480</v>
       </c>
       <c r="J15" t="n">
-        <v>1.034749133677824</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>260.52</v>
+        <v>54.86</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1290,40 +1278,40 @@
         <v>288</v>
       </c>
       <c r="B16" t="n">
-        <v>40.46</v>
+        <v>0.02</v>
       </c>
       <c r="C16" t="n">
-        <v>5.075099316124292</v>
+        <v>0.1035070342035747</v>
       </c>
       <c r="D16" t="n">
-        <v>5.07</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>41.11561287398877</v>
+        <v>3.007034203574591</v>
       </c>
       <c r="F16" t="n">
-        <v>41.03</v>
+        <v>3.01</v>
       </c>
       <c r="G16" t="n">
-        <v>2.038552552863778</v>
+        <v>0.001341191920419399</v>
       </c>
       <c r="H16" t="n">
-        <v>96.96856825838911</v>
+        <v>0.1876804866557449</v>
       </c>
       <c r="I16" t="n">
         <v>480</v>
       </c>
       <c r="J16" t="n">
-        <v>2.020178505383107</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>814.74</v>
+        <v>53.76</v>
       </c>
       <c r="M16" t="n">
-        <v>114.641825670425</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1342,43 +1330,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B17" t="n">
-        <v>72.11</v>
+        <v>1.77</v>
       </c>
       <c r="C17" t="n">
-        <v>6.847233185818407</v>
+        <v>1.070440125731112</v>
       </c>
       <c r="D17" t="n">
-        <v>6.85</v>
+        <v>1.07</v>
       </c>
       <c r="E17" t="n">
-        <v>55.1930312391971</v>
+        <v>8.831901940027869</v>
       </c>
       <c r="F17" t="n">
-        <v>55.11</v>
+        <v>8.83</v>
       </c>
       <c r="G17" t="n">
-        <v>2.966539527927826</v>
+        <v>0.1414496286910074</v>
       </c>
       <c r="H17" t="n">
-        <v>153.5503720515275</v>
+        <v>7.866217683172112</v>
       </c>
       <c r="I17" t="n">
         <v>480</v>
       </c>
       <c r="J17" t="n">
-        <v>3.198966084406823</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1874.33</v>
+        <v>9.26</v>
       </c>
       <c r="M17" t="n">
-        <v>657.7220498556389</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1397,43 +1385,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B18" t="n">
-        <v>107.01</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>8.385859246508797</v>
+        <v>2.280141436057199</v>
       </c>
       <c r="D18" t="n">
-        <v>8.380000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="E18" t="n">
-        <v>66.43025061874503</v>
+        <v>18.04112514073551</v>
       </c>
       <c r="F18" t="n">
-        <v>66.34</v>
+        <v>18.04</v>
       </c>
       <c r="G18" t="n">
-        <v>3.922045988485321</v>
+        <v>0.6372816200648672</v>
       </c>
       <c r="H18" t="n">
-        <v>210.3284643495859</v>
+        <v>26.28922457090611</v>
       </c>
       <c r="I18" t="n">
         <v>480</v>
       </c>
       <c r="J18" t="n">
-        <v>4.381843007283041</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>3306.59</v>
+        <v>42.57</v>
       </c>
       <c r="M18" t="n">
-        <v>1513.222821725394</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1452,46 +1440,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B19" t="n">
-        <v>139.14</v>
+        <v>22.98</v>
       </c>
       <c r="C19" t="n">
-        <v>9.68461773578986</v>
+        <v>3.886221516983889</v>
       </c>
       <c r="D19" t="n">
-        <v>9.67</v>
+        <v>3.89</v>
       </c>
       <c r="E19" t="n">
-        <v>75.46307029436909</v>
+        <v>32.50912443755347</v>
       </c>
       <c r="F19" t="n">
-        <v>75.37</v>
+        <v>32.51</v>
       </c>
       <c r="G19" t="n">
-        <v>4.743865275118496</v>
+        <v>1.436935231600668</v>
       </c>
       <c r="H19" t="n">
-        <v>258.3635775844544</v>
+        <v>61.20627147992189</v>
       </c>
       <c r="I19" t="n">
         <v>480</v>
       </c>
       <c r="J19" t="n">
-        <v>5.382574533009467</v>
+        <v>1.275130655831706</v>
       </c>
       <c r="K19" t="n">
         <v>25</v>
       </c>
       <c r="L19" t="n">
-        <v>4858.59</v>
+        <v>285.98</v>
       </c>
       <c r="M19" t="n">
-        <v>2534.088219467551</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3524.314927590141</v>
+        <v>0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1510,25 +1498,25 @@
         <v>600</v>
       </c>
       <c r="B20" t="n">
-        <v>0.84</v>
+        <v>0.03</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5070968559646395</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06706436196316939</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H20" t="n">
-        <v>5.009820593176953</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I20" t="n">
         <v>480</v>
@@ -1540,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>112.33</v>
+        <v>111.96</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1562,40 +1550,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B21" t="n">
-        <v>34.68</v>
+        <v>0.03</v>
       </c>
       <c r="C21" t="n">
-        <v>3.288402894698747</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D21" t="n">
-        <v>3.29</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>25.72840067638389</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.526233600520957</v>
+        <v>0.002577086142916147</v>
       </c>
       <c r="H21" t="n">
-        <v>98.65935823598954</v>
+        <v>0.3648502350411618</v>
       </c>
       <c r="I21" t="n">
         <v>480</v>
       </c>
       <c r="J21" t="n">
-        <v>2.055403296583115</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>517.48</v>
+        <v>109.53</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1617,43 +1605,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B22" t="n">
-        <v>78.78</v>
+        <v>0.03</v>
       </c>
       <c r="C22" t="n">
-        <v>4.981718197901798</v>
+        <v>0.1035070138681873</v>
       </c>
       <c r="D22" t="n">
-        <v>4.98</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>41.01073239761079</v>
+        <v>3.007013868187967</v>
       </c>
       <c r="F22" t="n">
-        <v>40.93</v>
+        <v>3.01</v>
       </c>
       <c r="G22" t="n">
-        <v>4.024824946914554</v>
+        <v>0.002696353530537708</v>
       </c>
       <c r="H22" t="n">
-        <v>190.202636099845</v>
+        <v>0.3773158594038812</v>
       </c>
       <c r="I22" t="n">
         <v>480</v>
       </c>
       <c r="J22" t="n">
-        <v>3.96255491874677</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>1586.77</v>
+        <v>108.08</v>
       </c>
       <c r="M22" t="n">
-        <v>118.8638968584364</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1672,43 +1660,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B23" t="n">
-        <v>130</v>
+        <v>3.54</v>
       </c>
       <c r="C23" t="n">
-        <v>6.466513496232491</v>
+        <v>1.070428539916257</v>
       </c>
       <c r="D23" t="n">
-        <v>6.46</v>
+        <v>1.07</v>
       </c>
       <c r="E23" t="n">
-        <v>54.88691814952399</v>
+        <v>8.831813957763682</v>
       </c>
       <c r="F23" t="n">
-        <v>54.81</v>
+        <v>8.83</v>
       </c>
       <c r="G23" t="n">
-        <v>5.541002880690506</v>
+        <v>0.2818970309616283</v>
       </c>
       <c r="H23" t="n">
-        <v>283.1395307284893</v>
+        <v>15.67676713316368</v>
       </c>
       <c r="I23" t="n">
         <v>480</v>
       </c>
       <c r="J23" t="n">
-        <v>5.898740223510193</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>3372.46</v>
+        <v>18.45</v>
       </c>
       <c r="M23" t="n">
-        <v>1075.411035837808</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1727,43 +1715,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B24" t="n">
-        <v>176.54</v>
+        <v>15.78</v>
       </c>
       <c r="C24" t="n">
-        <v>7.636798771725837</v>
+        <v>2.279056988948726</v>
       </c>
       <c r="D24" t="n">
-        <v>7.62</v>
+        <v>2.28</v>
       </c>
       <c r="E24" t="n">
-        <v>65.92068986499801</v>
+        <v>18.03284435012896</v>
       </c>
       <c r="F24" t="n">
-        <v>65.83</v>
+        <v>18.03</v>
       </c>
       <c r="G24" t="n">
-        <v>6.8071827014116</v>
+        <v>1.257547147001177</v>
       </c>
       <c r="H24" t="n">
-        <v>360.0523877232297</v>
+        <v>51.88624801058367</v>
       </c>
       <c r="I24" t="n">
         <v>480</v>
       </c>
       <c r="J24" t="n">
-        <v>7.50109141090062</v>
+        <v>1.080963500220493</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>5431.69</v>
+        <v>83.94</v>
       </c>
       <c r="M24" t="n">
-        <v>2246.959204792479</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1782,46 +1770,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B25" t="n">
-        <v>218</v>
+        <v>44.75</v>
       </c>
       <c r="C25" t="n">
-        <v>8.571727941316917</v>
+        <v>3.880186275237719</v>
       </c>
       <c r="D25" t="n">
-        <v>8.550000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="E25" t="n">
-        <v>74.90163661148108</v>
+        <v>32.45143458336219</v>
       </c>
       <c r="F25" t="n">
-        <v>74.81</v>
+        <v>32.45</v>
       </c>
       <c r="G25" t="n">
-        <v>7.891593663265681</v>
+        <v>2.802007180776713</v>
       </c>
       <c r="H25" t="n">
-        <v>424.7893766656783</v>
+        <v>119.2627681788644</v>
       </c>
       <c r="I25" t="n">
         <v>480</v>
       </c>
       <c r="J25" t="n">
-        <v>8.849778680534966</v>
+        <v>2.484641003726341</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>7578.22</v>
+        <v>555.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3572.026317156186</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1566.308768586436</v>
+        <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1840,25 +1828,25 @@
         <v>300</v>
       </c>
       <c r="B26" t="n">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5097095487738532</v>
+        <v>0.09999999999999966</v>
       </c>
       <c r="D26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.5</v>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02712381863514086</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="H26" t="n">
-        <v>2.52565659092397</v>
+        <v>0.1849785005584436</v>
       </c>
       <c r="I26" t="n">
         <v>490</v>
@@ -1870,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>56.17</v>
+        <v>55.98</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1892,28 +1880,28 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B27" t="n">
-        <v>7.05</v>
+        <v>0.02</v>
       </c>
       <c r="C27" t="n">
-        <v>2.097237263179879</v>
+        <v>0.1004999999999997</v>
       </c>
       <c r="D27" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>19.52585550552578</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>19.46</v>
+        <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4500144915207483</v>
+        <v>0.001050962813729674</v>
       </c>
       <c r="H27" t="n">
-        <v>23.96578578479281</v>
+        <v>0.1858436461282929</v>
       </c>
       <c r="I27" t="n">
         <v>490</v>
@@ -1925,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>117.78</v>
+        <v>55.79</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1947,40 +1935,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B28" t="n">
-        <v>20.15</v>
+        <v>1.11</v>
       </c>
       <c r="C28" t="n">
-        <v>3.587961376096077</v>
+        <v>0.8333169274993898</v>
       </c>
       <c r="D28" t="n">
-        <v>3.59</v>
+        <v>0.83</v>
       </c>
       <c r="E28" t="n">
-        <v>32.01404898250903</v>
+        <v>7.622967438357835</v>
       </c>
       <c r="F28" t="n">
-        <v>31.96</v>
+        <v>7.62</v>
       </c>
       <c r="G28" t="n">
-        <v>1.106115934429251</v>
+        <v>0.0705646671083475</v>
       </c>
       <c r="H28" t="n">
-        <v>55.38760041241222</v>
+        <v>5.411070953559411</v>
       </c>
       <c r="I28" t="n">
         <v>490</v>
       </c>
       <c r="J28" t="n">
-        <v>1.130359192090045</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>10</v>
       </c>
       <c r="L28" t="n">
-        <v>348.78</v>
+        <v>58.35</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2002,43 +1990,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B29" t="n">
-        <v>41.31</v>
+        <v>4.47</v>
       </c>
       <c r="C29" t="n">
-        <v>5.155448601251658</v>
+        <v>1.686852311125221</v>
       </c>
       <c r="D29" t="n">
-        <v>5.16</v>
+        <v>1.69</v>
       </c>
       <c r="E29" t="n">
-        <v>43.70760840031978</v>
+        <v>15.62005066646548</v>
       </c>
       <c r="F29" t="n">
-        <v>43.66</v>
+        <v>15.62</v>
       </c>
       <c r="G29" t="n">
-        <v>1.751207451778249</v>
+        <v>0.2851876053516663</v>
       </c>
       <c r="H29" t="n">
-        <v>98.40848152157649</v>
+        <v>16.5520263813256</v>
       </c>
       <c r="I29" t="n">
         <v>490</v>
       </c>
       <c r="J29" t="n">
-        <v>2.008336357583194</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>15</v>
       </c>
       <c r="L29" t="n">
-        <v>879.92</v>
+        <v>43.64</v>
       </c>
       <c r="M29" t="n">
-        <v>147.6514346855556</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2057,43 +2045,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B30" t="n">
-        <v>67.08</v>
+        <v>10.67</v>
       </c>
       <c r="C30" t="n">
-        <v>6.627628611801459</v>
+        <v>2.624134776843007</v>
       </c>
       <c r="D30" t="n">
-        <v>6.63</v>
+        <v>2.62</v>
       </c>
       <c r="E30" t="n">
-        <v>55.31344932090792</v>
+        <v>24.45105493091729</v>
       </c>
       <c r="F30" t="n">
-        <v>55.26</v>
+        <v>24.45</v>
       </c>
       <c r="G30" t="n">
-        <v>2.458375492156354</v>
+        <v>0.680572899672278</v>
       </c>
       <c r="H30" t="n">
-        <v>144.6897894941094</v>
+        <v>33.17348435095675</v>
       </c>
       <c r="I30" t="n">
         <v>490</v>
       </c>
       <c r="J30" t="n">
-        <v>2.952852846818559</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>1751.45</v>
+        <v>88.75</v>
       </c>
       <c r="M30" t="n">
-        <v>582.949161618786</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2112,43 +2100,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B31" t="n">
-        <v>95.04000000000001</v>
+        <v>24.68</v>
       </c>
       <c r="C31" t="n">
-        <v>7.931428299597067</v>
+        <v>4.027282967115957</v>
       </c>
       <c r="D31" t="n">
-        <v>7.93</v>
+        <v>4.03</v>
       </c>
       <c r="E31" t="n">
-        <v>65.78485352416976</v>
+        <v>34.80472850071433</v>
       </c>
       <c r="F31" t="n">
-        <v>65.73</v>
+        <v>34.8</v>
       </c>
       <c r="G31" t="n">
-        <v>3.186898437712939</v>
+        <v>1.23943726633993</v>
       </c>
       <c r="H31" t="n">
-        <v>190.9584013198435</v>
+        <v>64.81099612824386</v>
       </c>
       <c r="I31" t="n">
         <v>490</v>
       </c>
       <c r="J31" t="n">
-        <v>3.897110231017213</v>
+        <v>1.322673390372324</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>2915.23</v>
+        <v>327.85</v>
       </c>
       <c r="M31" t="n">
-        <v>1257.55064255063</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2170,25 +2158,25 @@
         <v>600</v>
       </c>
       <c r="B32" t="n">
-        <v>0.84</v>
+        <v>0.03</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5077554292862827</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05383248647581229</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H32" t="n">
-        <v>5.020267337861309</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I32" t="n">
         <v>490</v>
@@ -2200,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>112.33</v>
+        <v>111.96</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2222,28 +2210,28 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B33" t="n">
-        <v>14.17</v>
+        <v>0.03</v>
       </c>
       <c r="C33" t="n">
-        <v>2.096922510475909</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D33" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="E33" t="n">
-        <v>19.52201310220779</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>19.46</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9043494575680633</v>
+        <v>0.002080836072668816</v>
       </c>
       <c r="H33" t="n">
-        <v>48.16451636866918</v>
+        <v>0.3679579883208992</v>
       </c>
       <c r="I33" t="n">
         <v>490</v>
@@ -2255,7 +2243,7 @@
         <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>236.71</v>
+        <v>110.46</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2277,40 +2265,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B34" t="n">
-        <v>40.84</v>
+        <v>2.21</v>
       </c>
       <c r="C34" t="n">
-        <v>3.577694014237756</v>
+        <v>0.8333108486808261</v>
       </c>
       <c r="D34" t="n">
-        <v>3.58</v>
+        <v>0.83</v>
       </c>
       <c r="E34" t="n">
-        <v>31.97258295115358</v>
+        <v>7.622910483697379</v>
       </c>
       <c r="F34" t="n">
-        <v>31.92</v>
+        <v>7.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.246870089196137</v>
+        <v>0.1411272752245907</v>
       </c>
       <c r="H34" t="n">
-        <v>112.3799910139852</v>
+        <v>10.82201520138165</v>
       </c>
       <c r="I34" t="n">
         <v>490</v>
       </c>
       <c r="J34" t="n">
-        <v>2.293469204367045</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>706.73</v>
+        <v>116.69</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2332,43 +2320,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B35" t="n">
-        <v>78.78</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>5.016414244611714</v>
+        <v>1.686378338560889</v>
       </c>
       <c r="D35" t="n">
-        <v>5.02</v>
+        <v>1.69</v>
       </c>
       <c r="E35" t="n">
-        <v>43.57629832164762</v>
+        <v>15.61560984524403</v>
       </c>
       <c r="F35" t="n">
-        <v>43.52</v>
+        <v>15.62</v>
       </c>
       <c r="G35" t="n">
-        <v>3.3979375142526</v>
+        <v>0.567085692101544</v>
       </c>
       <c r="H35" t="n">
-        <v>189.689497998181</v>
+        <v>32.91678578309956</v>
       </c>
       <c r="I35" t="n">
         <v>490</v>
       </c>
       <c r="J35" t="n">
-        <v>3.871214244860837</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>1678.89</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>152.1337940921464</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2387,43 +2375,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B36" t="n">
-        <v>119.72</v>
+        <v>21.08</v>
       </c>
       <c r="C36" t="n">
-        <v>6.222019606608034</v>
+        <v>2.622194323078295</v>
       </c>
       <c r="D36" t="n">
-        <v>6.22</v>
+        <v>2.62</v>
       </c>
       <c r="E36" t="n">
-        <v>55.02107186680634</v>
+        <v>24.4278994235578</v>
       </c>
       <c r="F36" t="n">
-        <v>54.97</v>
+        <v>24.43</v>
       </c>
       <c r="G36" t="n">
-        <v>4.539538464693192</v>
+        <v>1.344776462325282</v>
       </c>
       <c r="H36" t="n">
-        <v>264.754235284915</v>
+        <v>65.56822642459238</v>
       </c>
       <c r="I36" t="n">
         <v>490</v>
       </c>
       <c r="J36" t="n">
-        <v>5.403147658875815</v>
+        <v>1.338127069889641</v>
       </c>
       <c r="K36" t="n">
         <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>3122.4</v>
+        <v>175.11</v>
       </c>
       <c r="M36" t="n">
-        <v>925.0115882875585</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2442,43 +2430,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B37" t="n">
-        <v>157.37</v>
+        <v>49.05</v>
       </c>
       <c r="C37" t="n">
-        <v>7.197318038838813</v>
+        <v>4.021713438196871</v>
       </c>
       <c r="D37" t="n">
-        <v>7.19</v>
+        <v>4.02</v>
       </c>
       <c r="E37" t="n">
-        <v>65.28720447046373</v>
+        <v>34.73766623137995</v>
       </c>
       <c r="F37" t="n">
-        <v>65.23</v>
+        <v>34.74</v>
       </c>
       <c r="G37" t="n">
-        <v>5.527299818225743</v>
+        <v>2.465697127250822</v>
       </c>
       <c r="H37" t="n">
-        <v>328.5595983587621</v>
+        <v>128.8708351140339</v>
       </c>
       <c r="I37" t="n">
         <v>490</v>
       </c>
       <c r="J37" t="n">
-        <v>6.705297925689023</v>
+        <v>2.630017043143549</v>
       </c>
       <c r="K37" t="n">
         <v>25</v>
       </c>
       <c r="L37" t="n">
-        <v>4809.54</v>
+        <v>650.0700000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>1841.488202734779</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2500,25 +2488,25 @@
         <v>300</v>
       </c>
       <c r="B38" t="n">
-        <v>0.41</v>
+        <v>0.02</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4989144616429525</v>
+        <v>0.09999999999999966</v>
       </c>
       <c r="D38" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02598707967019179</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="H38" t="n">
-        <v>2.440355704831624</v>
+        <v>0.1849785005584436</v>
       </c>
       <c r="I38" t="n">
         <v>490</v>
@@ -2530,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>56.16</v>
+        <v>55.98</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2555,25 +2543,25 @@
         <v>294</v>
       </c>
       <c r="B39" t="n">
-        <v>12.2</v>
+        <v>0.02</v>
       </c>
       <c r="C39" t="n">
-        <v>2.757773579560554</v>
+        <v>0.1004999999999998</v>
       </c>
       <c r="D39" t="n">
-        <v>2.76</v>
+        <v>0.1</v>
       </c>
       <c r="E39" t="n">
-        <v>25.73387101115816</v>
+        <v>0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7781235892385338</v>
+        <v>0.001033388184737539</v>
       </c>
       <c r="H39" t="n">
-        <v>37.1915170757212</v>
+        <v>0.1827358928485557</v>
       </c>
       <c r="I39" t="n">
         <v>490</v>
@@ -2585,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>198.26</v>
+        <v>54.86</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2610,37 +2598,37 @@
         <v>290</v>
       </c>
       <c r="B40" t="n">
-        <v>30.67</v>
+        <v>1.81</v>
       </c>
       <c r="C40" t="n">
-        <v>4.40378383679282</v>
+        <v>1.07110083413834</v>
       </c>
       <c r="D40" t="n">
-        <v>4.4</v>
+        <v>1.07</v>
       </c>
       <c r="E40" t="n">
-        <v>41.2556918743084</v>
+        <v>9.850851282631947</v>
       </c>
       <c r="F40" t="n">
-        <v>41.18</v>
+        <v>9.85</v>
       </c>
       <c r="G40" t="n">
-        <v>1.444156995058768</v>
+        <v>0.115782454155323</v>
       </c>
       <c r="H40" t="n">
-        <v>77.75686043222797</v>
+        <v>8.040364209851047</v>
       </c>
       <c r="I40" t="n">
         <v>490</v>
       </c>
       <c r="J40" t="n">
-        <v>1.58687470269853</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>10</v>
       </c>
       <c r="L40" t="n">
-        <v>633.16</v>
+        <v>10.54</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2662,43 +2650,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B41" t="n">
-        <v>56.52</v>
+        <v>7.56</v>
       </c>
       <c r="C41" t="n">
-        <v>6.072725384883319</v>
+        <v>2.205136009785341</v>
       </c>
       <c r="D41" t="n">
-        <v>6.07</v>
+        <v>2.21</v>
       </c>
       <c r="E41" t="n">
-        <v>56.78745811564818</v>
+        <v>20.49580577595799</v>
       </c>
       <c r="F41" t="n">
-        <v>56.71</v>
+        <v>20.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.172571187323559</v>
+        <v>0.4822804533158526</v>
       </c>
       <c r="H41" t="n">
-        <v>126.1935232604214</v>
+        <v>25.18016937248927</v>
       </c>
       <c r="I41" t="n">
         <v>490</v>
       </c>
       <c r="J41" t="n">
-        <v>2.575378025722885</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>15</v>
       </c>
       <c r="L41" t="n">
-        <v>1521.78</v>
+        <v>47.38</v>
       </c>
       <c r="M41" t="n">
-        <v>429.8847873513319</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2717,43 +2705,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B42" t="n">
-        <v>86.27</v>
+        <v>19.69</v>
       </c>
       <c r="C42" t="n">
-        <v>7.570491128207317</v>
+        <v>3.591010148406546</v>
       </c>
       <c r="D42" t="n">
-        <v>7.57</v>
+        <v>3.59</v>
       </c>
       <c r="E42" t="n">
-        <v>72.18614204612471</v>
+        <v>34.29627000743794</v>
       </c>
       <c r="F42" t="n">
-        <v>72.11</v>
+        <v>34.3</v>
       </c>
       <c r="G42" t="n">
-        <v>2.957053579720867</v>
+        <v>1.080244760499608</v>
       </c>
       <c r="H42" t="n">
-        <v>176.5644191671016</v>
+        <v>54.11039776714537</v>
       </c>
       <c r="I42" t="n">
         <v>490</v>
       </c>
       <c r="J42" t="n">
-        <v>3.603355493206156</v>
+        <v>1.104293831982559</v>
       </c>
       <c r="K42" t="n">
         <v>20</v>
       </c>
       <c r="L42" t="n">
-        <v>2903.31</v>
+        <v>257.21</v>
       </c>
       <c r="M42" t="n">
-        <v>1193.151360814117</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2775,43 +2763,43 @@
         <v>272</v>
       </c>
       <c r="B43" t="n">
-        <v>116.44</v>
+        <v>41.93</v>
       </c>
       <c r="C43" t="n">
-        <v>8.859223418840811</v>
+        <v>5.316451894699596</v>
       </c>
       <c r="D43" t="n">
-        <v>8.859999999999999</v>
+        <v>5.32</v>
       </c>
       <c r="E43" t="n">
-        <v>86.08119708972042</v>
+        <v>48.5346369626788</v>
       </c>
       <c r="F43" t="n">
-        <v>86</v>
+        <v>48.53</v>
       </c>
       <c r="G43" t="n">
-        <v>3.717717311297023</v>
+        <v>1.74353962629283</v>
       </c>
       <c r="H43" t="n">
-        <v>223.9437410860026</v>
+        <v>98.671569251788</v>
       </c>
       <c r="I43" t="n">
         <v>490</v>
       </c>
       <c r="J43" t="n">
-        <v>4.570280430326584</v>
+        <v>2.013705494934449</v>
       </c>
       <c r="K43" t="n">
         <v>25</v>
       </c>
       <c r="L43" t="n">
-        <v>4641</v>
+        <v>797.63</v>
       </c>
       <c r="M43" t="n">
-        <v>2262.444621253327</v>
+        <v>376.5761545420159</v>
       </c>
       <c r="N43" t="n">
-        <v>862.8223557648652</v>
+        <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2830,25 +2818,25 @@
         <v>600</v>
       </c>
       <c r="B44" t="n">
-        <v>0.87</v>
+        <v>0.03</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5165235699647456</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D44" t="n">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0.05570774464392109</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H44" t="n">
-        <v>5.160133427713635</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I44" t="n">
         <v>490</v>
@@ -2860,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>112.35</v>
+        <v>111.96</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2882,40 +2870,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B45" t="n">
-        <v>24.17</v>
+        <v>0.03</v>
       </c>
       <c r="C45" t="n">
-        <v>2.757252038991461</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D45" t="n">
-        <v>2.76</v>
+        <v>0.1</v>
       </c>
       <c r="E45" t="n">
-        <v>25.72816254764867</v>
+        <v>0.5</v>
       </c>
       <c r="F45" t="n">
-        <v>25.65</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.542430220463972</v>
+        <v>0.00206326144367668</v>
       </c>
       <c r="H45" t="n">
-        <v>73.72814099161297</v>
+        <v>0.3648502350411618</v>
       </c>
       <c r="I45" t="n">
         <v>490</v>
       </c>
       <c r="J45" t="n">
-        <v>1.504655938604347</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>392.99</v>
+        <v>109.53</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2937,40 +2925,40 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B46" t="n">
-        <v>59.72</v>
+        <v>3.64</v>
       </c>
       <c r="C46" t="n">
-        <v>4.379169272770713</v>
+        <v>1.071092854020358</v>
       </c>
       <c r="D46" t="n">
-        <v>4.38</v>
+        <v>1.07</v>
       </c>
       <c r="E46" t="n">
-        <v>41.18008836812327</v>
+        <v>9.850776514006128</v>
       </c>
       <c r="F46" t="n">
-        <v>41.11</v>
+        <v>9.85</v>
       </c>
       <c r="G46" t="n">
-        <v>2.822867226485536</v>
+        <v>0.231960701718961</v>
       </c>
       <c r="H46" t="n">
-        <v>151.7294345511315</v>
+        <v>16.10826119109404</v>
       </c>
       <c r="I46" t="n">
         <v>490</v>
       </c>
       <c r="J46" t="n">
-        <v>3.096519072472071</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>10</v>
       </c>
       <c r="L46" t="n">
-        <v>1231.91</v>
+        <v>21.11</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2995,40 +2983,40 @@
         <v>564</v>
       </c>
       <c r="B47" t="n">
-        <v>104</v>
+        <v>14.94</v>
       </c>
       <c r="C47" t="n">
-        <v>5.814510897552293</v>
+        <v>2.204107834269932</v>
       </c>
       <c r="D47" t="n">
-        <v>5.81</v>
+        <v>2.2</v>
       </c>
       <c r="E47" t="n">
-        <v>56.54483781874343</v>
+        <v>20.4861288388611</v>
       </c>
       <c r="F47" t="n">
-        <v>56.47</v>
+        <v>20.49</v>
       </c>
       <c r="G47" t="n">
-        <v>4.098024176193424</v>
+        <v>0.9535178295967187</v>
       </c>
       <c r="H47" t="n">
-        <v>236.2233216407843</v>
+        <v>49.79294453889717</v>
       </c>
       <c r="I47" t="n">
         <v>490</v>
       </c>
       <c r="J47" t="n">
-        <v>4.820884115118046</v>
+        <v>1.016182541610146</v>
       </c>
       <c r="K47" t="n">
         <v>15</v>
       </c>
       <c r="L47" t="n">
-        <v>2797.34</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>715.0082311900215</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3047,43 +3035,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B48" t="n">
-        <v>146.48</v>
+        <v>38.68</v>
       </c>
       <c r="C48" t="n">
-        <v>6.968936153320366</v>
+        <v>3.587525434517818</v>
       </c>
       <c r="D48" t="n">
-        <v>6.97</v>
+        <v>3.59</v>
       </c>
       <c r="E48" t="n">
-        <v>71.6720502346577</v>
+        <v>34.24152884816219</v>
       </c>
       <c r="F48" t="n">
-        <v>71.59</v>
+        <v>34.24</v>
       </c>
       <c r="G48" t="n">
-        <v>5.229392465277148</v>
+        <v>2.123286703730921</v>
       </c>
       <c r="H48" t="n">
-        <v>309.7471655162448</v>
+        <v>106.3157374148358</v>
       </c>
       <c r="I48" t="n">
         <v>490</v>
       </c>
       <c r="J48" t="n">
-        <v>6.321370724821323</v>
+        <v>2.169708926833383</v>
       </c>
       <c r="K48" t="n">
         <v>20</v>
       </c>
       <c r="L48" t="n">
-        <v>4910.52</v>
+        <v>504.22</v>
       </c>
       <c r="M48" t="n">
-        <v>1807.687212491644</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3102,43 +3090,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="B49" t="n">
-        <v>184.43</v>
+        <v>79.72</v>
       </c>
       <c r="C49" t="n">
-        <v>7.891400478608174</v>
+        <v>5.222154371956973</v>
       </c>
       <c r="D49" t="n">
-        <v>7.88</v>
+        <v>5.22</v>
       </c>
       <c r="E49" t="n">
-        <v>85.38681068009068</v>
+        <v>48.37954657635696</v>
       </c>
       <c r="F49" t="n">
-        <v>85.3</v>
+        <v>48.38</v>
       </c>
       <c r="G49" t="n">
-        <v>6.197192316294479</v>
+        <v>3.352118448456039</v>
       </c>
       <c r="H49" t="n">
-        <v>371.3061427991291</v>
+        <v>188.9355001318654</v>
       </c>
       <c r="I49" t="n">
         <v>490</v>
       </c>
       <c r="J49" t="n">
-        <v>7.577676383655696</v>
+        <v>3.855826533303376</v>
       </c>
       <c r="K49" t="n">
         <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>7313.32</v>
+        <v>1511.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3183.929013236973</v>
+        <v>637.1072941055788</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
